--- a/outputs/2026-10-04_sttv_linea-base-sast_plataforma-ansv.xlsx
+++ b/outputs/2026-10-04_sttv_linea-base-sast_plataforma-ansv.xlsx
@@ -559,7 +559,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Validado por Santiago Torreglosa. Versión del cálculo: 2feda89.</t>
+          <t>Validado por Santiago Torreglosa. Versión del cálculo: aae977d.</t>
         </is>
       </c>
     </row>
